--- a/data/fmsForecastOutput/File1/RPT_RPT5219538410918ZM_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT5219538410918ZM_fmsForecastOutput.xlsx
@@ -1911,7 +1911,7 @@
         <v>55410467.85654642</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>64457296.43036578</v>
+        <v>64457296.43036576</v>
       </c>
       <c r="P8" s="152" t="n">
         <v>74042493.58908701</v>
@@ -1931,13 +1931,13 @@
         <v>389.8704220475512</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>428.9428113684872</v>
+        <v>428.9428113684871</v>
       </c>
       <c r="W8" s="149" t="n">
         <v>461.9655681602156</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>500.5494956714866</v>
+        <v>500.5494956714865</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>46.26989379859481</v>
@@ -1946,7 +1946,7 @@
         <v>53.17241563229771</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>60.91527445543133</v>
+        <v>60.91527445543132</v>
       </c>
       <c r="AB8" s="149" t="n">
         <v>68.95211170070326</v>
@@ -1961,7 +1961,7 @@
         <v>55410467.85654642</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>64457296.43036578</v>
+        <v>64457296.43036576</v>
       </c>
       <c r="AG8" s="152" t="n">
         <v>74042493.58908701</v>
@@ -2025,7 +2025,7 @@
         <v>550.1991098219373</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>606.8032727787472</v>
+        <v>606.8032727787473</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>665.8009218871562</v>
@@ -2040,7 +2040,7 @@
         <v>62.44396997308113</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>70.04254821614126</v>
+        <v>70.04254821614127</v>
       </c>
       <c r="J9" s="156" t="n">
         <v>79.43263813965828</v>
@@ -2075,7 +2075,7 @@
         <v>556.9930772043903</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>614.2961995560346</v>
+        <v>614.2961995560347</v>
       </c>
       <c r="V9" s="156" t="n">
         <v>674.0223632994703</v>
@@ -2090,7 +2090,7 @@
         <v>62.72131460770862</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>70.35484150852272</v>
+        <v>70.35484150852274</v>
       </c>
       <c r="AA9" s="156" t="n">
         <v>79.78952239896928</v>
@@ -2173,25 +2173,25 @@
         <v>342.9830243778948</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>378.1046296252325</v>
+        <v>378.1046296252326</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>415.110739450819</v>
+        <v>415.1107394508189</v>
       </c>
       <c r="F10" s="162" t="n">
         <v>445.6407889586572</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>481.4620221317311</v>
+        <v>481.462022131731</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>42.12793791789213</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>48.07572374059487</v>
+        <v>48.07572374059488</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>54.91278158565106</v>
+        <v>54.91278158565105</v>
       </c>
       <c r="K10" s="162" t="n">
         <v>62.02199844996622</v>
@@ -2203,10 +2203,10 @@
         <v>65111535.07752347</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>75414171.34491178</v>
+        <v>75414171.3449118</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>87334913.73666851</v>
+        <v>87334913.7366685</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>99956085.98567449</v>
@@ -2226,7 +2226,7 @@
         <v>431.7054311111228</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>474.0998535894216</v>
+        <v>474.0998535894215</v>
       </c>
       <c r="W10" s="162" t="n">
         <v>508.9981653037589</v>
@@ -2241,7 +2241,7 @@
         <v>56.8555793556645</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>64.93923638439675</v>
+        <v>64.93923638439674</v>
       </c>
       <c r="AB10" s="162" t="n">
         <v>73.33766865071324</v>
@@ -2253,10 +2253,10 @@
         <v>65111535.07752347</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>75414171.34491178</v>
+        <v>75414171.3449118</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>87334913.73666851</v>
+        <v>87334913.7366685</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>99956085.98567449</v>
@@ -2327,10 +2327,10 @@
         <v>824.7878903133743</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>874.1644087084682</v>
+        <v>874.1644087084683</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>928.448942169601</v>
+        <v>928.4489421696011</v>
       </c>
       <c r="H11" s="155" t="n">
         <v>120.2709688986606</v>
@@ -2345,7 +2345,7 @@
         <v>174.4523311576863</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>198.8771666116091</v>
+        <v>198.8771666116092</v>
       </c>
       <c r="M11" s="158" t="n">
         <v>8225347.283844909</v>
@@ -2380,7 +2380,7 @@
         <v>1111.825086216868</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1180.868055130275</v>
+        <v>1180.868055130276</v>
       </c>
       <c r="Y11" s="155" t="n">
         <v>138.863788892117</v>
@@ -2389,7 +2389,7 @@
         <v>156.9221372500337</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>178.5973718321608</v>
+        <v>178.5973718321609</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>202.0565921774845</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>363.8569495207904</v>
+        <v>363.8569495207903</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>400.5954795349116</v>
+        <v>400.5954795349118</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>439.4384161359094</v>
@@ -2473,28 +2473,28 @@
         <v>471.5815058937587</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>509.0617527638312</v>
+        <v>509.0617527638311</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>45.43918653984222</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>51.80396771401291</v>
+        <v>51.80396771401292</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>59.16172002266089</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>66.85700661818808</v>
+        <v>66.85700661818809</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>76.63628460615207</v>
+        <v>76.63628460615206</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>73336882.3613684</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>84869084.89653304</v>
+        <v>84869084.89653306</v>
       </c>
       <c r="O12" s="165" t="n">
         <v>98289905.792271</v>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>417.6771936160774</v>
+        <v>417.6771936160773</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>460.1406367978277</v>
@@ -2529,7 +2529,7 @@
         <v>53.68019002332777</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>61.20358017222152</v>
+        <v>61.20358017222154</v>
       </c>
       <c r="AA12" s="162" t="n">
         <v>69.89701636445885</v>
@@ -2544,7 +2544,7 @@
         <v>73336882.3613684</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>84869084.89653304</v>
+        <v>84869084.89653306</v>
       </c>
       <c r="AF12" s="165" t="n">
         <v>98289905.792271</v>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>3209.812768059382</v>
+        <v>3209.81276805938</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>3305.9118784958</v>
+        <v>3305.911878495799</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>3479.547699358201</v>
+        <v>3479.5476993582</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>3625.884961160802</v>
+        <v>3625.884961160801</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3840.484076832168</v>
+        <v>3840.484076832166</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2820.330162583948</v>
+        <v>2820.330162583947</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2903.88716527619</v>
+        <v>2903.887165276189</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>3058.99814380203</v>
+        <v>3058.998143802028</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>3187.531147187758</v>
+        <v>3187.531147187756</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3388.721821267638</v>
+        <v>3388.721821267635</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>69181528.77413526</v>
+        <v>69181528.77413523</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>78576830.33966155</v>
+        <v>78576830.33966152</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>91552316.14418438</v>
+        <v>91552316.14418435</v>
       </c>
       <c r="P13" s="159" t="n">
         <v>105696187.4316451</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>125113292.9968061</v>
+        <v>125113292.996806</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>2333.953299674144</v>
+        <v>2333.953299674143</v>
       </c>
       <c r="U13" s="156" t="n">
         <v>2403.829909964541</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>2530.085840240638</v>
+        <v>2530.085840240637</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>2636.492151053575</v>
+        <v>2636.492151053574</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>2792.533749215437</v>
+        <v>2792.533749215435</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>2040.878803226025</v>
+        <v>2040.878803226024</v>
       </c>
       <c r="Z13" s="156" t="n">
         <v>2101.321035605943</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>2213.628355424478</v>
+        <v>2213.628355424477</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>2306.637641970869</v>
+        <v>2306.637641970868</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>2452.545577101909</v>
+        <v>2452.545577101907</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>69181528.77413526</v>
+        <v>69181528.77413523</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>78576830.33966155</v>
+        <v>78576830.33966152</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>91552316.14418438</v>
+        <v>91552316.14418435</v>
       </c>
       <c r="AG13" s="159" t="n">
         <v>105696187.4316451</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>125113292.9968061</v>
+        <v>125113292.996806</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,31 +2746,31 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>638.7886600278506</v>
+        <v>638.7886600278504</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>693.6670163280271</v>
+        <v>693.667016328027</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>759.419968667421</v>
+        <v>759.4199686674209</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>814.8034130925719</v>
+        <v>814.8034130925716</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>882.6584700370881</v>
+        <v>882.6584700370878</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>86.98175081777943</v>
+        <v>86.9817508177794</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>98.14608420420738</v>
+        <v>98.14608420420737</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>112.2459606771623</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>127.1173298495458</v>
+        <v>127.1173298495457</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>146.5055993898356</v>
@@ -2785,7 +2785,7 @@
         <v>189842221.9364554</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>218286366.5970434</v>
+        <v>218286366.5970433</v>
       </c>
       <c r="Q14" s="172" t="n">
         <v>256411098.5460379</v>
@@ -2796,19 +2796,19 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>694.4528293624943</v>
+        <v>694.452829362494</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>752.7567050392141</v>
+        <v>752.7567050392139</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>822.3954565696356</v>
+        <v>822.3954565696354</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>880.7865644582513</v>
+        <v>880.7865644582512</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>952.5167538995755</v>
+        <v>952.5167538995753</v>
       </c>
       <c r="Y14" s="167" t="n">
         <v>101.7930913716058</v>
@@ -2823,7 +2823,7 @@
         <v>148.3622074838843</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>170.7832965679116</v>
+        <v>170.7832965679115</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>142518411.1355036</v>
@@ -2835,7 +2835,7 @@
         <v>189842221.9364554</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>218286366.5970434</v>
+        <v>218286366.5970433</v>
       </c>
       <c r="AH14" s="172" t="n">
         <v>256411098.5460379</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="C23" s="85" t="n">
-        <v>201554.1614855923</v>
+        <v>201554.1614855924</v>
       </c>
       <c r="D23" s="86" t="n">
         <v>211857.3204946432</v>
@@ -3712,10 +3712,10 @@
         <v>223671.6276573142</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>238750.2006721261</v>
+        <v>238750.200672126</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>257921.1752530636</v>
+        <v>257921.1752530637</v>
       </c>
       <c r="H23" s="85" t="n">
         <v>1412402.600197735</v>
@@ -3742,7 +3742,7 @@
         <v>1661376.744195786</v>
       </c>
       <c r="P23" s="86" t="n">
-        <v>1684044.573045075</v>
+        <v>1684044.573045074</v>
       </c>
       <c r="Q23" s="87" t="n">
         <v>1713259.015934754</v>
@@ -3843,7 +3843,7 @@
         <v>21553.13526775011</v>
       </c>
       <c r="D24" s="80" t="n">
-        <v>23768.57981326903</v>
+        <v>23768.57981326902</v>
       </c>
       <c r="E24" s="80" t="n">
         <v>26311.55657416943</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="C25" s="91" t="n">
-        <v>223107.2967533425</v>
+        <v>223107.2967533424</v>
       </c>
       <c r="D25" s="92" t="n">
         <v>235625.9003079122</v>
@@ -3954,7 +3954,7 @@
         <v>267900.6531999435</v>
       </c>
       <c r="G25" s="93" t="n">
-        <v>290498.6551992911</v>
+        <v>290498.6551992912</v>
       </c>
       <c r="H25" s="91" t="n">
         <v>1415379.0500445</v>
@@ -4007,7 +4007,7 @@
         <v>269193.2687759018</v>
       </c>
       <c r="Y25" s="91" t="n">
-        <v>1194855.374187104</v>
+        <v>1194855.374187103</v>
       </c>
       <c r="Z25" s="92" t="n">
         <v>1206932.845514507</v>
@@ -4022,10 +4022,10 @@
         <v>1232189.499322128</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>1400079.40828937</v>
+        <v>1400079.408289369</v>
       </c>
       <c r="AE25" s="92" t="n">
-        <v>1424062.648732508</v>
+        <v>1424062.648732507</v>
       </c>
       <c r="AF25" s="92" t="n">
         <v>1447568.806076962</v>
@@ -4414,7 +4414,7 @@
         <v>350.2537801471804</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>387.8149181787845</v>
+        <v>387.8149181787844</v>
       </c>
       <c r="F35" s="149" t="n">
         <v>422.970205261525</v>
@@ -4444,7 +4444,7 @@
         <v>58312864.66497567</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>68266434.39100206</v>
+        <v>68266434.39100204</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>79412930.37978922</v>
@@ -4464,13 +4464,13 @@
         <v>410.2918101430514</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>454.2914132523854</v>
+        <v>454.2914132523853</v>
       </c>
       <c r="W35" s="149" t="n">
         <v>495.4727714299193</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>538.2041578077308</v>
+        <v>538.2041578077307</v>
       </c>
       <c r="Y35" s="148" t="n">
         <v>47.57456853187857</v>
@@ -4479,7 +4479,7 @@
         <v>55.95758340650233</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>64.51509475756627</v>
+        <v>64.51509475756626</v>
       </c>
       <c r="AB35" s="149" t="n">
         <v>73.95333383037833</v>
@@ -4494,7 +4494,7 @@
         <v>58312864.66497567</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>68266434.39100206</v>
+        <v>68266434.39100204</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>79412930.37978922</v>
@@ -4513,7 +4513,7 @@
         <v>565.9086046083704</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>638.8115762007227</v>
+        <v>638.8115762007228</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>705.4030879692489</v>
@@ -4528,7 +4528,7 @@
         <v>64.2268940149862</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>73.73722693051934</v>
+        <v>73.73722693051936</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>84.15733049819283</v>
@@ -4543,7 +4543,7 @@
         <v>18191941.16370313</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>21058880.08272808</v>
+        <v>21058880.08272809</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>24238389.22827421</v>
@@ -4563,7 +4563,7 @@
         <v>572.8965559382135</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>646.6997478367067</v>
+        <v>646.6997478367068</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>714.1135447576934</v>
@@ -4578,7 +4578,7 @@
         <v>64.51215749937907</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>74.06599340112449</v>
+        <v>74.0659934011245</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>84.53544240866009</v>
@@ -4593,7 +4593,7 @@
         <v>18191941.16370313</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>21058880.08272808</v>
+        <v>21058880.08272809</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>24238389.22827421</v>
@@ -4615,25 +4615,25 @@
         <v>352.6872406269887</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>397.9467468160924</v>
+        <v>397.9467468160925</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>439.6837884462558</v>
+        <v>439.6837884462557</v>
       </c>
       <c r="F37" s="162" t="n">
         <v>478.0091880397895</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>517.7313269920802</v>
+        <v>517.7313269920801</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>43.31988792890257</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>50.59863425201017</v>
+        <v>50.59863425201019</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>58.16341893164002</v>
+        <v>58.16341893164001</v>
       </c>
       <c r="K37" s="162" t="n">
         <v>66.52686615368111</v>
@@ -4645,10 +4645,10 @@
         <v>66953773.24032705</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>79371744.74770375</v>
+        <v>79371744.74770376</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>92504823.61927627</v>
+        <v>92504823.61927626</v>
       </c>
       <c r="P37" s="165" t="n">
         <v>107216234.8812291</v>
@@ -4668,7 +4668,7 @@
         <v>454.3604030021783</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>502.1648440216012</v>
+        <v>502.1648440216011</v>
       </c>
       <c r="W37" s="162" t="n">
         <v>545.9684251056387</v>
@@ -4680,10 +4680,10 @@
         <v>51.22909120227973</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>59.83923779340303</v>
+        <v>59.83923779340304</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>68.78340346017798</v>
+        <v>68.78340346017796</v>
       </c>
       <c r="AB37" s="162" t="n">
         <v>78.66443178681021</v>
@@ -4695,10 +4695,10 @@
         <v>66953773.24032705</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>79371744.74770375</v>
+        <v>79371744.74770376</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>92504823.61927627</v>
+        <v>92504823.61927626</v>
       </c>
       <c r="AG37" s="165" t="n">
         <v>107216234.8812291</v>
@@ -4720,13 +4720,13 @@
         <v>802.3898184552372</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>873.7820185630105</v>
+        <v>873.7820185630106</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>937.8388397236423</v>
+        <v>937.8388397236424</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>998.5916384034792</v>
+        <v>998.5916384034794</v>
       </c>
       <c r="H38" s="155" t="n">
         <v>123.6967833481126</v>
@@ -4735,7 +4735,7 @@
         <v>142.9612665200117</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>163.5829476219391</v>
+        <v>163.5829476219392</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>187.1594979275484</v>
@@ -4776,7 +4776,7 @@
         <v>1192.810801315761</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1270.080574549747</v>
+        <v>1270.080574549748</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>142.8192037262081</v>
@@ -4788,10 +4788,10 @@
         <v>189.2064298013173</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>216.7744626508145</v>
+        <v>216.7744626508146</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>248.1540168809688</v>
+        <v>248.1540168809689</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>8459639.181838185</v>
@@ -4819,13 +4819,13 @@
         <v>374.1595403752356</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>421.6266840314249</v>
+        <v>421.626684031425</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>465.4616512575342</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>505.845018512008</v>
+        <v>505.8450185120081</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>547.4226098276002</v>
@@ -4834,22 +4834,22 @@
         <v>46.72579477501641</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>54.5236684954323</v>
+        <v>54.52366849543231</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>62.66523563216846</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>71.71460994073387</v>
+        <v>71.71460994073388</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>82.41128841210252</v>
+        <v>82.41128841210251</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>75413412.42216524</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>89324699.52793923</v>
+        <v>89324699.52793925</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>104110565.1488338</v>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>429.5037019203073</v>
+        <v>429.5037019203072</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>484.2979534028133</v>
@@ -4884,7 +4884,7 @@
         <v>55.20014184925167</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>64.41675924257734</v>
+        <v>64.41675924257736</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>74.03626870190085</v>
@@ -4899,7 +4899,7 @@
         <v>75413412.42216524</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>89324699.52793923</v>
+        <v>89324699.52793925</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>104110565.1488338</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>3301.597169367807</v>
+        <v>3301.597169367805</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>3686.742635471711</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437093</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>2900.977332425374</v>
+        <v>2900.977332425372</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100517</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>97003937.42761643</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>2400.692552637465</v>
+        <v>2400.692552637464</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>2530.613654031521</v>
+        <v>2530.61365403152</v>
       </c>
       <c r="V40" s="156" t="n">
         <v>2680.743632380417</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>2828.85423932787</v>
+        <v>2828.854239327869</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>3003.693394875161</v>
+        <v>3003.693394875159</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>2099.237608749254</v>
+        <v>2099.237608749253</v>
       </c>
       <c r="Z40" s="156" t="n">
         <v>2212.149737452303</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>2345.442207485143</v>
+        <v>2345.442207485142</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>2474.933092243421</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>2637.996748523081</v>
+        <v>2637.99674852308</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100517</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>97003937.42761643</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5026,16 +5026,16 @@
         <v>730.1653162186612</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>804.5121242644021</v>
+        <v>804.512124264402</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>874.124505895719</v>
+        <v>874.1245058957189</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>949.2839689357266</v>
+        <v>949.283968935726</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>89.45645662511875</v>
+        <v>89.45645662511873</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>103.3101833037134</v>
@@ -5047,22 +5047,22 @@
         <v>136.3720025714879</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>157.5642466267241</v>
+        <v>157.564246626724</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>146573182.8131705</v>
+        <v>146573182.8131704</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>172045860.0076335</v>
+        <v>172045860.0076334</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>201114502.5764503</v>
+        <v>201114502.5764502</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>234178526.107541</v>
+        <v>234178526.1075409</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>275765716.3780742</v>
+        <v>275765716.3780741</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,19 +5070,19 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>714.2106111223356</v>
+        <v>714.2106111223355</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>792.3640949229716</v>
+        <v>792.3640949229714</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>871.226914023882</v>
+        <v>871.2269140238818</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>944.9115063650139</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1024.415348987214</v>
+        <v>1024.415348987213</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>104.689192588194</v>
@@ -5100,19 +5100,19 @@
         <v>183.6744914339316</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>146573182.8131705</v>
+        <v>146573182.8131704</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>172045860.0076335</v>
+        <v>172045860.0076334</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>201114502.5764503</v>
+        <v>201114502.5764502</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>234178526.107541</v>
+        <v>234178526.1075409</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>275765716.3780742</v>
+        <v>275765716.3780741</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5404,7 +5404,7 @@
         <v>16233.04970876887</v>
       </c>
       <c r="N46" s="152" t="n">
-        <v>19628.59781623222</v>
+        <v>19628.59781623223</v>
       </c>
       <c r="O46" s="152" t="n">
         <v>23757.72589699713</v>
@@ -5454,7 +5454,7 @@
         <v>16233.04970876887</v>
       </c>
       <c r="AE46" s="152" t="n">
-        <v>19628.59781623222</v>
+        <v>19628.59781623223</v>
       </c>
       <c r="AF46" s="152" t="n">
         <v>23757.72589699713</v>
@@ -5593,7 +5593,7 @@
         <v>0.01072352958126649</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.01273976587192697</v>
+        <v>0.01273976587192698</v>
       </c>
       <c r="J48" s="162" t="n">
         <v>0.01517172264316162</v>
@@ -5637,7 +5637,7 @@
         <v>0.1483272616838144</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.1662563205568682</v>
+        <v>0.1662563205568681</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.01268139649462298</v>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="C49" s="155" t="n">
-        <v>0.05511847987654938</v>
+        <v>0.05511847987654939</v>
       </c>
       <c r="D49" s="156" t="n">
-        <v>0.06002765782677747</v>
+        <v>0.06002765782677748</v>
       </c>
       <c r="E49" s="156" t="n">
         <v>0.06501912662649774</v>
@@ -5692,7 +5692,7 @@
         <v>0.07390165411824727</v>
       </c>
       <c r="H49" s="155" t="n">
-        <v>0.009441786196499305</v>
+        <v>0.009441786196499307</v>
       </c>
       <c r="I49" s="156" t="n">
         <v>0.01069508833707209</v>
@@ -5707,10 +5707,10 @@
         <v>0.01583000519619676</v>
       </c>
       <c r="M49" s="158" t="n">
-        <v>645.7249921338652</v>
+        <v>645.7249921338653</v>
       </c>
       <c r="N49" s="159" t="n">
-        <v>744.5914070340302</v>
+        <v>744.5914070340303</v>
       </c>
       <c r="O49" s="159" t="n">
         <v>863.5965974050199</v>
@@ -5727,10 +5727,10 @@
         </is>
       </c>
       <c r="T49" s="155" t="n">
-        <v>0.07010364186689812</v>
+        <v>0.07010364186689813</v>
       </c>
       <c r="U49" s="156" t="n">
-        <v>0.07634748701020522</v>
+        <v>0.07634748701020523</v>
       </c>
       <c r="V49" s="156" t="n">
         <v>0.08269599556684744</v>
@@ -5757,10 +5757,10 @@
         <v>0.01836485668246825</v>
       </c>
       <c r="AD49" s="158" t="n">
-        <v>645.7249921338652</v>
+        <v>645.7249921338653</v>
       </c>
       <c r="AE49" s="159" t="n">
-        <v>744.5914070340302</v>
+        <v>744.5914070340303</v>
       </c>
       <c r="AF49" s="159" t="n">
         <v>863.5965974050199</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.08543437829440999</v>
+        <v>0.08543437829440997</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.09784356153829185</v>
+        <v>0.09784356153829188</v>
       </c>
       <c r="E50" s="162" t="n">
         <v>0.1117403837389542</v>
@@ -5803,7 +5803,7 @@
         <v>0.01504363991687091</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.01789373289604699</v>
+        <v>0.017893732896047</v>
       </c>
       <c r="L50" s="163" t="n">
         <v>0.02124693432614474</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>0.09807148499249578</v>
+        <v>0.09807148499249577</v>
       </c>
       <c r="U50" s="162" t="n">
         <v>0.1123871861087075</v>
@@ -5847,7 +5847,7 @@
         <v>0.01260422170693418</v>
       </c>
       <c r="Z50" s="162" t="n">
-        <v>0.01494868656505309</v>
+        <v>0.0149486865650531</v>
       </c>
       <c r="AA50" s="162" t="n">
         <v>0.01777341066229635</v>
@@ -5986,7 +5986,7 @@
         <v>0.07718104575580055</v>
       </c>
       <c r="D52" s="180" t="n">
-        <v>0.08797366820908514</v>
+        <v>0.08797366820908517</v>
       </c>
       <c r="E52" s="180" t="n">
         <v>0.09997933894145931</v>
@@ -5995,7 +5995,7 @@
         <v>0.1124814121024787</v>
       </c>
       <c r="G52" s="181" t="n">
-        <v>0.1253069545890618</v>
+        <v>0.1253069545890617</v>
       </c>
       <c r="H52" s="179" t="n">
         <v>0.01050948914699579</v>
@@ -6007,7 +6007,7 @@
         <v>0.01477743200122038</v>
       </c>
       <c r="K52" s="180" t="n">
-        <v>0.01754820430845324</v>
+        <v>0.01754820430845323</v>
       </c>
       <c r="L52" s="181" t="n">
         <v>0.02079872466302172</v>
@@ -6036,7 +6036,7 @@
         <v>0.08390661724635966</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.09546766251311567</v>
+        <v>0.09546766251311568</v>
       </c>
       <c r="V52" s="186" t="n">
         <v>0.1082702029031056</v>
@@ -6051,7 +6051,7 @@
         <v>0.01229905559443363</v>
       </c>
       <c r="Z52" s="186" t="n">
-        <v>0.01455615368720263</v>
+        <v>0.01455615368720264</v>
       </c>
       <c r="AA52" s="186" t="n">
         <v>0.01726560658189257</v>
@@ -6340,7 +6340,7 @@
         <v>0.006312652989907676</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.0059135112887804</v>
+        <v>0.005913511288780401</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.0002182438534425569</v>
@@ -6358,7 +6358,7 @@
         <v>0.0007992417272445699</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.101437433010594e-05</v>
+        <v>3.101437433010593e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6423,7 +6423,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6577,7 +6577,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>0.0007740115133016669</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.006362358699137e-05</v>
+        <v>3.006362358699136e-05</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6745,7 +6745,7 @@
         <v>0.005268227716249657</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.004960780226548961</v>
+        <v>0.004960780226548962</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0.004653902074605053</v>
@@ -6781,7 +6781,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.006047482591033662</v>
+        <v>0.006047482591033661</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.005698158589079581</v>
@@ -6816,7 +6816,7 @@
         <v>0.0007402490486099231</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>2.87449117944655e-05</v>
+        <v>2.874491179446549e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
@@ -6831,7 +6831,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,16 +6946,16 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.004759294004793454</v>
+        <v>0.004759294004793455</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.004460365371489598</v>
+        <v>0.004460365371489599</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0.004164063495649975</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0001529500751459861</v>
+        <v>0.000152950075145986</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>0.0006310915540558638</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006154688139292611</v>
+        <v>0.0006154688139292612</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>2.386171294871122e-05</v>
@@ -6985,7 +6985,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0007584092827714785</v>
+        <v>0.0007584092827714786</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.000738013603049626</v>
+        <v>0.0007380136030496262</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0.0007190993945259967</v>
@@ -7035,7 +7035,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7303,13 +7303,13 @@
         <v>0.00423130770579009</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.005664116158427142</v>
+        <v>0.005664116158427144</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.007022073357940787</v>
+        <v>0.007022073357940786</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.00833311895691425</v>
+        <v>0.008333118956914248</v>
       </c>
       <c r="H68" s="148" t="n">
         <v>0.0003570298447330324</v>
@@ -7318,13 +7318,13 @@
         <v>0.0005490464510592812</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0007655346816305533</v>
+        <v>0.0007655346816305535</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.0009978984895167367</v>
+        <v>0.0009978984895167365</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.00125515799160005</v>
+        <v>0.001255157991600049</v>
       </c>
       <c r="M68" s="151" t="n">
         <v>450.6865261022976</v>
@@ -7333,7 +7333,7 @@
         <v>704.4597020478225</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>997.0452295340143</v>
+        <v>997.0452295340147</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1318.398827527651</v>
@@ -7347,28 +7347,28 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.003347907992705035</v>
+        <v>0.003347907992705034</v>
       </c>
       <c r="U68" s="149" t="n">
         <v>0.004956608597204411</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.006635018958325115</v>
+        <v>0.006635018958325118</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.008225747593005713</v>
+        <v>0.008225747593005711</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.009761523371804923</v>
+        <v>0.00976152337180492</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004397131139116245</v>
+        <v>0.0004397131139116244</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.0006760062768368415</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009422561473262578</v>
+        <v>0.0009422561473262581</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.001227759612287846</v>
@@ -7383,7 +7383,7 @@
         <v>704.4597020478225</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>997.0452295340143</v>
+        <v>997.0452295340147</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1318.398827527651</v>
@@ -7507,13 +7507,13 @@
         <v>0.003531955201237717</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.0047390461018341</v>
+        <v>0.004739046101834101</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.005877904160290899</v>
+        <v>0.005877904160290898</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.006976396845718806</v>
+        <v>0.006976396845718803</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>0.0002915995448342948</v>
@@ -7522,10 +7522,10 @@
         <v>0.0004490854890805339</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006269030858094162</v>
+        <v>0.0006269030858094164</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008180565418405471</v>
+        <v>0.0008180565418405469</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.001030109009122541</v>
@@ -7537,7 +7537,7 @@
         <v>704.4597020478225</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>997.0452295340143</v>
+        <v>997.0452295340147</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1318.398827527651</v>
@@ -7557,13 +7557,13 @@
         <v>0.004032651608436553</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.005412485993509827</v>
+        <v>0.005412485993509829</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.00671357404336917</v>
+        <v>0.006713574043369169</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.007968397356289649</v>
+        <v>0.007968397356289647</v>
       </c>
       <c r="Y70" s="161" t="n">
         <v>0.0003448388347951523</v>
@@ -7572,10 +7572,10 @@
         <v>0.0005310999746912964</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007413685212064234</v>
+        <v>0.0007413685212064236</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.0009673077472898337</v>
+        <v>0.0009673077472898336</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.00121782983159106</v>
@@ -7587,7 +7587,7 @@
         <v>704.4597020478225</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>997.0452295340143</v>
+        <v>997.0452295340147</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1318.398827527651</v>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.006483527712111258</v>
+        <v>0.006483527712111256</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.009695372243502838</v>
+        <v>0.00969537224350284</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.01299893853538077</v>
@@ -7621,19 +7621,19 @@
         <v>0.001110627190625366</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.001727418099574823</v>
+        <v>0.001727418099574824</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.002433564248748223</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003214363362248185</v>
+        <v>0.003214363362248186</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.004074829975022104</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.95593873923131</v>
+        <v>75.9559387392313</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>120.2627442393418</v>
@@ -7642,10 +7642,10 @@
         <v>172.6544121934863</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>302.9560444208731</v>
+        <v>302.956044420873</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.00824621625599903</v>
+        <v>0.008246216255999028</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>0.012331270837786</v>
@@ -7662,13 +7662,13 @@
         <v>0.01653298374293271</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02048588172280477</v>
+        <v>0.02048588172280478</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>0.02419501760595788</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001282320256909175</v>
+        <v>0.001282320256909174</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>0.001995987245632264</v>
@@ -7677,13 +7677,13 @@
         <v>0.00281475551022546</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003722984397433852</v>
+        <v>0.003722984397433853</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.004727330633769203</v>
+        <v>0.004727330633769202</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.95593873923131</v>
+        <v>75.9559387392313</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>120.2627442393418</v>
@@ -7692,10 +7692,10 @@
         <v>172.6544121934863</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>302.9560444208731</v>
+        <v>302.956044420873</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,37 +7705,37 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.002612907919934835</v>
+        <v>0.002612907919934834</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.003892820150663698</v>
+        <v>0.003892820150663699</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.005229539633518427</v>
+        <v>0.005229539633518428</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.006497115909970407</v>
+        <v>0.006497115909970408</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.007720238158554335</v>
+        <v>0.007720238158554333</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003263051881837593</v>
+        <v>0.0003263051881837592</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.0005034093985173547</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007040544210179798</v>
+        <v>0.0007040544210179799</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009211084742790706</v>
+        <v>0.0009211084742790707</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001162236930065987</v>
+        <v>0.001162236930065986</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>526.642464841529</v>
+        <v>526.6424648415289</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>824.7224462871643</v>
@@ -7755,19 +7755,19 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.002999398660965374</v>
+        <v>0.002999398660965373</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.004471455207496178</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.006009088254150192</v>
+        <v>0.006009088254150194</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.007466914211959671</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.008873874140013572</v>
+        <v>0.008873874140013571</v>
       </c>
       <c r="Y72" s="161" t="n">
         <v>0.0003854849930454488</v>
@@ -7776,7 +7776,7 @@
         <v>0.0005947509204641971</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008318098826152078</v>
+        <v>0.0008318098826152079</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001088182840221264</v>
@@ -7785,7 +7785,7 @@
         <v>0.001372900780484588</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>526.642464841529</v>
+        <v>526.6424648415289</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>824.7224462871643</v>
@@ -7915,31 +7915,31 @@
         <v>0.003500134939365452</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.004679113298454358</v>
+        <v>0.004679113298454359</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>0.005790160302960489</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.006854465118683072</v>
+        <v>0.00685446511868307</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003214201118433284</v>
+        <v>0.0003214201118433283</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.0004952297433767576</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0006915956769268277</v>
+        <v>0.0006915956769268279</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009033218384782982</v>
+        <v>0.0009033218384782981</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.001137719236600299</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>526.642464841529</v>
+        <v>526.6424648415289</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>824.7224462871643</v>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.002566183181932267</v>
+        <v>0.002566183181932266</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.003798292238395006</v>
@@ -7971,16 +7971,16 @@
         <v>0.006259050120507662</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.007396963929085197</v>
+        <v>0.007396963929085196</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0003761518537616276</v>
+        <v>0.0003761518537616275</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0005791335423488648</v>
+        <v>0.000579133542348865</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008080442441264598</v>
+        <v>0.00080804424412646</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.001054292299749089</v>
@@ -7989,7 +7989,7 @@
         <v>0.00132625266614081</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>526.642464841529</v>
+        <v>526.6424648415289</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>824.7224462871643</v>
@@ -8266,7 +8266,7 @@
         <v>350.3822224588424</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>387.9614611168862</v>
+        <v>387.9614611168861</v>
       </c>
       <c r="F79" s="149" t="n">
         <v>423.130517841733</v>
@@ -8281,7 +8281,7 @@
         <v>45.46493167869708</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>52.43500403485944</v>
+        <v>52.43500403485943</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>60.13057441862465</v>
@@ -8296,7 +8296,7 @@
         <v>58334248.7001003</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>68292230.10798058</v>
+        <v>68292230.10798056</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>79443029.17070332</v>
@@ -8316,7 +8316,7 @@
         <v>410.4422691289004</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>454.4630755462575</v>
+        <v>454.4630755462574</v>
       </c>
       <c r="W79" s="149" t="n">
         <v>495.6605636607258</v>
@@ -8331,7 +8331,7 @@
         <v>55.97810373140712</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>64.53947296246382</v>
+        <v>64.5394729624638</v>
       </c>
       <c r="AB79" s="149" t="n">
         <v>73.98136334549277</v>
@@ -8346,7 +8346,7 @@
         <v>58334248.7001003</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>68292230.10798058</v>
+        <v>68292230.10798056</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>79443029.17070332</v>
@@ -8365,7 +8365,7 @@
         <v>565.9192085784429</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>638.8223657606205</v>
+        <v>638.8223657606206</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>705.4139092635714</v>
@@ -8380,7 +8380,7 @@
         <v>64.22809749564799</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>73.73847235601929</v>
+        <v>73.7384723560193</v>
       </c>
       <c r="J80" s="156" t="n">
         <v>84.15862152067099</v>
@@ -8395,7 +8395,7 @@
         <v>18192282.0434814</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>21059235.76827997</v>
+        <v>21059235.76827998</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>24238761.05928575</v>
@@ -8415,7 +8415,7 @@
         <v>572.9072908482049</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>646.7106706282233</v>
+        <v>646.7106706282234</v>
       </c>
       <c r="V80" s="156" t="n">
         <v>714.1244996754976</v>
@@ -8430,7 +8430,7 @@
         <v>64.51336632529524</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>74.06724437950679</v>
+        <v>74.0672443795068</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>84.53673923159522</v>
@@ -8445,7 +8445,7 @@
         <v>18192282.0434814</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>21059235.76827997</v>
+        <v>21059235.76827998</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>24238761.05928575</v>
@@ -8470,13 +8470,13 @@
         <v>398.0557434262515</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>439.8081651672144</v>
+        <v>439.8081651672143</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>478.1451129027882</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>517.8838621529349</v>
+        <v>517.8838621529347</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>43.33159007675604</v>
@@ -8485,7 +8485,7 @@
         <v>50.61249309030016</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>58.17987206345101</v>
+        <v>58.17987206345099</v>
       </c>
       <c r="K81" s="162" t="n">
         <v>66.54578347869059</v>
@@ -8500,7 +8500,7 @@
         <v>79393484.46838027</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>92530991.16726634</v>
+        <v>92530991.16726631</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>107246722.4793802</v>
@@ -8520,7 +8520,7 @@
         <v>454.4848511704671</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>502.3068952373188</v>
+        <v>502.3068952373187</v>
       </c>
       <c r="W81" s="162" t="n">
         <v>546.1236745971567</v>
@@ -8535,7 +8535,7 @@
         <v>59.8556276096942</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>68.80286074835543</v>
+        <v>68.80286074835541</v>
       </c>
       <c r="AB81" s="162" t="n">
         <v>78.68680050352324</v>
@@ -8550,7 +8550,7 @@
         <v>79393484.46838027</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>92530991.16726634</v>
+        <v>92530991.16726631</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>107246722.4793802</v>
@@ -8572,13 +8572,13 @@
         <v>802.4595414853076</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>873.8600366281723</v>
+        <v>873.8600366281725</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>937.9245263542813</v>
+        <v>937.9245263542814</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>998.6845632146762</v>
+        <v>998.6845632146764</v>
       </c>
       <c r="H82" s="155" t="n">
         <v>123.7073357614998</v>
@@ -8590,7 +8590,7 @@
         <v>163.5975535817733</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>187.1765979516572</v>
+        <v>187.1765979516573</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>213.9218940858095</v>
@@ -8677,16 +8677,16 @@
         <v>465.5832750829813</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>505.9779021989667</v>
+        <v>505.9779021989668</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>547.5714642776339</v>
+        <v>547.5714642776338</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>46.73744820378872</v>
+        <v>46.73744820378873</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>54.53746629549102</v>
+        <v>54.53746629549101</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>62.68160988267768</v>
@@ -8695,13 +8695,13 @@
         <v>71.73344911366031</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>82.43369758335872</v>
+        <v>82.43369758335871</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>75432220.55232911</v>
+        <v>75432220.55232912</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>89347304.10276704</v>
+        <v>89347304.10276702</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>104137768.9478335</v>
@@ -8721,7 +8721,7 @@
         <v>429.6108202865517</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>484.4205102027186</v>
+        <v>484.4205102027185</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>534.9860954677596</v>
@@ -8730,10 +8730,10 @@
         <v>581.5031840618975</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>629.3951244598076</v>
+        <v>629.3951244598074</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>55.21390878300548</v>
+        <v>55.21390878300549</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>64.43306059553076</v>
@@ -8748,10 +8748,10 @@
         <v>97.37540154054319</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>75432220.55232911</v>
+        <v>75432220.55232912</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>89347304.10276704</v>
+        <v>89347304.10276702</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>104137768.9478335</v>
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>3301.597169367807</v>
+        <v>3301.597169367805</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>3686.742635471711</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437093</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>2900.977332425374</v>
+        <v>2900.977332425372</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100517</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>97003937.42761643</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>2400.692552637465</v>
+        <v>2400.692552637464</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>2530.613654031521</v>
+        <v>2530.61365403152</v>
       </c>
       <c r="V84" s="156" t="n">
         <v>2680.743632380417</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>2828.85423932787</v>
+        <v>2828.854239327869</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>3003.693394875161</v>
+        <v>3003.693394875159</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>2099.237608749254</v>
+        <v>2099.237608749253</v>
       </c>
       <c r="Z84" s="156" t="n">
         <v>2212.149737452303</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>2345.442207485143</v>
+        <v>2345.442207485142</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>2474.933092243421</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>2637.996748523081</v>
+        <v>2637.99674852308</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100517</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>97003937.42761643</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,22 +8872,22 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>657.0470490053042</v>
+        <v>657.047049005304</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>730.261250387181</v>
+        <v>730.2612503871811</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>804.6209467801377</v>
+        <v>804.6209467801376</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>874.2429304181996</v>
+        <v>874.2429304181995</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>949.4161303554343</v>
+        <v>949.4161303554339</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>89.46793559178859</v>
+        <v>89.46793559178856</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>103.3237569100115</v>
@@ -8896,7 +8896,7 @@
         <v>118.9268848313061</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>136.3904779593478</v>
+        <v>136.3904779593477</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>157.5861830706237</v>
@@ -8922,13 +8922,13 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>714.3022579425833</v>
+        <v>714.3022579425831</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>792.4682011971576</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>871.3447607308503</v>
+        <v>871.3447607308501</v>
       </c>
       <c r="W85" s="186" t="n">
         <v>945.0395209592427</v>
@@ -8949,7 +8949,7 @@
         <v>159.1851592051295</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>183.700063004027</v>
+        <v>183.7000630040269</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>146591990.9433343</v>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="C94" s="85" t="n">
-        <v>201554.1614855923</v>
+        <v>201554.1614855924</v>
       </c>
       <c r="D94" s="86" t="n">
         <v>211857.3204946432</v>
@@ -9765,10 +9765,10 @@
         <v>223671.6276573142</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>238750.2006721261</v>
+        <v>238750.200672126</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>257921.1752530636</v>
+        <v>257921.1752530637</v>
       </c>
       <c r="H94" s="85" t="n">
         <v>1412402.600197735</v>
@@ -9795,7 +9795,7 @@
         <v>1661376.744195786</v>
       </c>
       <c r="P94" s="86" t="n">
-        <v>1684044.573045075</v>
+        <v>1684044.573045074</v>
       </c>
       <c r="Q94" s="87" t="n">
         <v>1713259.015934754</v>
@@ -9871,7 +9871,7 @@
         <v>21553.13526775011</v>
       </c>
       <c r="D95" s="80" t="n">
-        <v>23768.57981326903</v>
+        <v>23768.57981326902</v>
       </c>
       <c r="E95" s="80" t="n">
         <v>26311.55657416943</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C96" s="132" t="n">
-        <v>223107.2967533425</v>
+        <v>223107.2967533424</v>
       </c>
       <c r="D96" s="133" t="n">
         <v>235625.9003079122</v>
@@ -10000,7 +10000,7 @@
         <v>267900.6531999435</v>
       </c>
       <c r="G96" s="134" t="n">
-        <v>290498.6551992911</v>
+        <v>290498.6551992912</v>
       </c>
       <c r="H96" s="132" t="n">
         <v>1415379.0500445</v>
@@ -10053,7 +10053,7 @@
         <v>269193.2687759018</v>
       </c>
       <c r="Y96" s="135" t="n">
-        <v>1194855.374187104</v>
+        <v>1194855.374187103</v>
       </c>
       <c r="Z96" s="136" t="n">
         <v>1206932.845514507</v>
@@ -10068,10 +10068,10 @@
         <v>1232189.499322128</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>1400079.40828937</v>
+        <v>1400079.408289369</v>
       </c>
       <c r="AE96" s="136" t="n">
-        <v>1424062.648732508</v>
+        <v>1424062.648732507</v>
       </c>
       <c r="AF96" s="136" t="n">
         <v>1447568.806076962</v>
